--- a/PRUEBAS A CALIFICAR/Ya procesadas/SANTIAGO DE LAS ATALAYAS-301_Ajustado_20260626_172342.xlsx
+++ b/PRUEBAS A CALIFICAR/Ya procesadas/SANTIAGO DE LAS ATALAYAS-301_Ajustado_20260626_172342.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\Ajustar 3 y 5\Ajustados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\PROYECTO JULIANA\PRUEBAS A CALIFICAR\Ya procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B0884F-F1A1-4E50-A49B-7941350B13A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC25B9D-62B5-488B-857C-BBD106CDEA96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$W$73</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="105">
   <si>
     <t>Est.</t>
   </si>
@@ -332,6 +335,9 @@
   </si>
   <si>
     <t>1011250291</t>
+  </si>
+  <si>
+    <t>1025560504</t>
   </si>
 </sst>
 </file>
@@ -399,28 +405,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4347,8 +4332,8 @@
       <c r="D52" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>81</v>
+      <c r="E52" t="s">
+        <v>104</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>26</v>
@@ -4418,8 +4403,8 @@
       <c r="D53" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>81</v>
+      <c r="E53" t="s">
+        <v>104</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>26</v>
@@ -5887,6 +5872,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W73" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>